--- a/docs/planning/QA엑셀-v1/윤성현/QA 담양 중대재해 공통 윤성현.xlsx
+++ b/docs/planning/QA엑셀-v1/윤성현/QA 담양 중대재해 공통 윤성현.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_정보" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'메뉴·화면'!$A$3:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'메뉴·화면'!$A$3:$I$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'메뉴·화면'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'계정·권한'!$A$3:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'계정·권한'!$A$3:$I$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'계정·권한'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'공통 동작'!$A$3:$I$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'공통 동작'!$3:$3</definedName>
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,9 +55,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -110,6 +110,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -286,7 +292,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -784,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -843,12 +849,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>어느 메뉴에도 속하지 않는 화면 맨 위(메뉴·알림·도움말·계정)와 모든 화면에 걸리는 공통 동작을 봅니다.</t>
+          <t>QA박안전1 (재난안전과 담당자) · QA하정수1 (내 부서 물순환사업소 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -858,15 +864,15 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18줄</t>
+          <t>어느 메뉴에도 속하지 않는 화면 맨 위(메뉴·알림·도움말·계정)와 모든 화면에 걸리는 공통 동작을 봅니다. 대부분 QA박안전1 창에서 하고, 권한 차이는 QA하정수1 창과 비교합니다.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -879,12 +885,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>줄 수</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>메뉴·화면 → 계정·권한 → 공통 동작</t>
+          <t>16줄</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -897,12 +903,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>메뉴·화면 → 계정·권한 → 공통 동작</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -915,10 +921,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -929,7 +939,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -943,10 +953,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -954,82 +964,78 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전1(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수1(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>결과 고르는 법</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1040,14 +1046,14 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1058,14 +1064,14 @@
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1076,14 +1082,14 @@
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>오류</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1094,14 +1100,14 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>보류</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -1112,14 +1118,14 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1129,256 +1135,216 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>주로 하는 것</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>정환경</t>
+          <t>QA하정수1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+          <t>담당 공무원 (내 부서: 물순환사업소)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>오순환</t>
+          <t>QA시스템관리</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="5" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과장</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>군수</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «윤성현_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전1 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
         </is>
       </c>
     </row>
@@ -1392,85 +1358,110 @@
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="51">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1570,36 +1561,36 @@
         </is>
       </c>
       <c r="B5" s="21">
-        <f>COUNTA('메뉴·화면'!$A$4:$A$9)</f>
-        <v>6</v>
+        <f>COUNTA('메뉴·화면'!$A$4:$A$8)</f>
+        <v>5</v>
       </c>
       <c r="C5" s="21">
-        <f>COUNTIF('메뉴·화면'!$G$4:$G$9,"성공")</f>
+        <f>COUNTIF('메뉴·화면'!$G$4:$G$8,"성공")</f>
         <v>0</v>
       </c>
       <c r="D5" s="21">
-        <f>COUNTIF('메뉴·화면'!$G$4:$G$9,"실패")</f>
+        <f>COUNTIF('메뉴·화면'!$G$4:$G$8,"실패")</f>
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <f>COUNTIF('메뉴·화면'!$G$4:$G$9,"오류")</f>
+        <f>COUNTIF('메뉴·화면'!$G$4:$G$8,"오류")</f>
         <v>0</v>
       </c>
       <c r="F5" s="21">
-        <f>COUNTIF('메뉴·화면'!$G$4:$G$9,"보류")</f>
+        <f>COUNTIF('메뉴·화면'!$G$4:$G$8,"보류")</f>
         <v>0</v>
       </c>
       <c r="G5" s="21">
-        <f>COUNTIF('메뉴·화면'!$G$4:$G$9,"확인 불가")</f>
+        <f>COUNTIF('메뉴·화면'!$G$4:$G$8,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H5" s="21">
-        <f>COUNTIF('메뉴·화면'!$G$4:$G$9,"문의")</f>
+        <f>COUNTIF('메뉴·화면'!$G$4:$G$8,"문의")</f>
         <v>0</v>
       </c>
       <c r="I5" s="21">
-        <f>COUNTBLANK('메뉴·화면'!$G$4:$G$9)</f>
-        <v>6</v>
+        <f>COUNTBLANK('메뉴·화면'!$G$4:$G$8)</f>
+        <v>5</v>
       </c>
       <c r="J5" s="22">
         <f>IF(B5=0,0,(B5-I5)/B5)</f>
@@ -1613,36 +1604,36 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTA('계정·권한'!$A$4:$A$8)</f>
-        <v>5</v>
+        <f>COUNTA('계정·권한'!$A$4:$A$7)</f>
+        <v>4</v>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIF('계정·권한'!$G$4:$G$8,"성공")</f>
+        <f>COUNTIF('계정·권한'!$G$4:$G$7,"성공")</f>
         <v>0</v>
       </c>
       <c r="D6" s="21">
-        <f>COUNTIF('계정·권한'!$G$4:$G$8,"실패")</f>
+        <f>COUNTIF('계정·권한'!$G$4:$G$7,"실패")</f>
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <f>COUNTIF('계정·권한'!$G$4:$G$8,"오류")</f>
+        <f>COUNTIF('계정·권한'!$G$4:$G$7,"오류")</f>
         <v>0</v>
       </c>
       <c r="F6" s="21">
-        <f>COUNTIF('계정·권한'!$G$4:$G$8,"보류")</f>
+        <f>COUNTIF('계정·권한'!$G$4:$G$7,"보류")</f>
         <v>0</v>
       </c>
       <c r="G6" s="21">
-        <f>COUNTIF('계정·권한'!$G$4:$G$8,"확인 불가")</f>
+        <f>COUNTIF('계정·권한'!$G$4:$G$7,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H6" s="21">
-        <f>COUNTIF('계정·권한'!$G$4:$G$8,"문의")</f>
+        <f>COUNTIF('계정·권한'!$G$4:$G$7,"문의")</f>
         <v>0</v>
       </c>
       <c r="I6" s="21">
-        <f>COUNTBLANK('계정·권한'!$G$4:$G$8)</f>
-        <v>5</v>
+        <f>COUNTBLANK('계정·권한'!$G$4:$G$7)</f>
+        <v>4</v>
       </c>
       <c r="J6" s="22">
         <f>IF(B6=0,0,(B6-I6)/B6)</f>
@@ -1700,7 +1691,7 @@
       </c>
       <c r="B8" s="24">
         <f>SUM(B5:B7)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="24">
         <f>SUM(C5:C7)</f>
@@ -1728,7 +1719,7 @@
       </c>
       <c r="I8" s="24">
         <f>SUM(I5:I7)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J8" s="25">
         <f>IF(B8=0,0,(B8-I8)/B8)</f>
@@ -1775,11 +1766,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1799,7 +1790,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요.</t>
+          <t>🗂 QA박안전1 창에서 합니다. 1번만 QA하정수1 창과 비교합니다.</t>
         </is>
       </c>
     </row>
@@ -1850,13 +1841,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전 → 홍길동 → 김담양</t>
+          <t>QA박안전1(재난안전과) → QA하정수1(담당 공무원)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1871,25 +1862,25 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>계정을 바꿔 가며 맨 위 메뉴를 센다</t>
+          <t>두 창에서 맨 위 메뉴를 센다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>박안전 11개, 홍길동·김담양 10개(«시스템 관리»는 박안전만)</t>
+          <t>QA하정수1 창은 10개이고 «시스템 관리»가 없다. QA박안전1 창은 시스템 관리 권한이 있으면 11개(맨 끝 «시스템 관리»), 없으면 10개다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1904,12 +1895,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>안전보건교육 · 인력·예산 · 시스템 관리의 왼쪽 메뉴를 본다</t>
+          <t>안전보건교육과 인력·예산의 왼쪽 메뉴를 본다(시스템 관리 권한이 있으면 시스템 관리도)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>묶음 제목(현업근로자 등)은 눌리지 않고, 지금 화면이 강조돼 있다</t>
+          <t>묶음 제목(현업근로자 · 관리감독자 · 교육 현황·관리 등)은 눌리지 않고, 지금 화면이 강조돼 있다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
@@ -1922,7 +1913,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1949,13 +1940,13 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1970,25 +1961,25 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>알림 목록 항목을 하나씩 누른다</t>
+          <t>알림을 몇 개 누르고, «해당 화면 바로 열기 →»도 눌러 본다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>모두 관련 화면으로 간다. «이전 버전 화면»으로 가는 알림이 없다</t>
+          <t>누를 때마다 내 할일이나 그 업무 화면으로 간다. 도착한 화면 제목 아래 안내가 «이전 버전 화면»이나 «메뉴에서 제외된 화면»으로 시작하면 실패. 알림이 없으면 «확인 불가»</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2003,333 +1994,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>[?] → «자주 하는 일» 버튼을 눌러 본다</t>
+          <t>① 통합 현황 · 이행 관리 · 문서 목록 화면에서 각각 [?]를 누른다
+② «자주 하는 일»의 [바로가기 →]를 하나씩 눌러 본다</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>지금 화면 설명이 나오고 버튼이 모두 동작한다</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>화면 맨 위 [?]</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>처음 상태로 되돌리기</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>무언가 등록한 뒤 [?] → «예시 데이터 되돌리기»</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>한 번 묻고 처음 상태로 돌아간다</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:I9"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G4:G9">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"성공"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
-      <formula>"실패"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
-      <formula>"오류"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
-      <formula>"보류"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
-      <formula>"확인 불가"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="6">
-      <formula>"문의"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H9">
-    <cfRule type="expression" priority="7" dxfId="7">
-      <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="G4:G9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
-      <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>공통 — 계정·권한</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>누구로</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>어디서</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>확인할 것</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>해 볼 것</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>이러면 성공</t>
-        </is>
-      </c>
-      <c r="G3" s="27" t="inlineStr">
-        <is>
-          <t>결과 ▼</t>
-        </is>
-      </c>
-      <c r="H3" s="27" t="inlineStr">
-        <is>
-          <t>메모 (실패·오류·문의일 때)</t>
-        </is>
-      </c>
-      <c r="I3" s="27" t="inlineStr">
-        <is>
-          <t>사진 (필요할 때 붙여넣기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>박안전 → 하정수</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>화면 오른쪽 위 이름</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>계정 바꾸기</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>이름을 눌러 하정수로 → 위험성평가·교육 화면 → 박안전으로 되돌린다</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>이름·메뉴·버튼이 바뀌고, 입력해 둔 데이터는 그대로다</t>
-        </is>
-      </c>
-      <c r="G4" s="29" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="51" customHeight="1">
-      <c r="A5" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>하정수</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>여러 화면 (위험성평가 2 · 이수현황 · 채용시교육 · 내 할일)</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>자기 부서만 보인다</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>다섯 화면을 차례로 연다</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>다섯 곳 모두 물순환사업소 것만 보이고 부서 조건에도 다른 부서가 없다</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="51" customHeight="1">
-      <c r="A6" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>여러 화면 (예산 총괄표 · 경영방침 · 의견청취 · 인력 평가 · 이행점검)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>과장은 상신하지 않는다</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>다섯 화면의 상신 버튼을 본다</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>상신 버튼이 없고 «상신은 담당자가 합니다…»가 보인다</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>결재선 지정 창 (예산·경영방침 등)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>결재선 조직도</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>검토 [조직도]를 연 채 결재 [조직도]를 누른다 → 같은 것을 다시 누른다</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>한 번에 하나만 열리고 다시 누르면 닫힌다. 군수·부군수도 목록에 있다</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="51" customHeight="1">
-      <c r="A8" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>박안전 → 홍길동 → 김중대</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>상신한 문서</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>기안자와 기본 결재선</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>박안전으로 상신 → 홍길동으로 같은 문서를 연다 → 김중대로 새 기안 창을 연다</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>문서의 기안자는 박안전 그대로다. 김중대의 기본 결재선은 «기안 김중대 → 검토 (미지정) → 결재 …»다(정상)</t>
+          <t>지금 화면 설명이 나오고 [바로가기 →]를 누르면 그 화면으로 간다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
@@ -2377,6 +2048,269 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>공통 — 계정·권한</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>🗂 QA박안전1 창과 QA하정수1 창을 나란히 두고 합니다. 8·9번은 결재선 창과 결재 상태 창만 열어 보고 [상신]은 누르지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>누구로</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>어디서</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>확인할 것</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>해 볼 것</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>이러면 성공</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>결과 ▼</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>메모 (실패·오류·문의일 때)</t>
+        </is>
+      </c>
+      <c r="I3" s="27" t="inlineStr">
+        <is>
+          <t>사진 (필요할 때 붙여넣기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전1(재난안전과) → QA하정수1(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>화면 오른쪽 위 이름</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>창마다 내 계정으로 보인다</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>① 두 창의 오른쪽 위 이름을 본다
+② 두 창을 모두 새로고침(F5)한다</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>각 창에 그 창에서 로그인한 계정 이름이 보이고, 새로고침해도 다른 계정으로 바뀌지 않는다</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="81" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수1(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>여러 화면 (정기·수시 위험성평가 · 이수현황 · 채용시교육 · 내 할일)</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>내 부서 것만 보인다</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>다섯 화면을 차례로 열고, 부서 조건이 있으면 펼쳐 본다</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>위험성평가 두 화면 · 채용시교육 · 내 할일에는 내 부서(물순환사업소) 것만 있고 부서 조건에도 다른 부서가 없다. 이수현황의 부서별 요약에는 다른 부서 완료율도 보이지만(정상) [상세]는 내 부서 줄에만 있다</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="141" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전1(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>결재선 조직도</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>① «작성중» 점검표 하나를 열어 [온나라 결재 상신]
+② 검토 [조직도]를 연 채 결재 [조직도]를 누른다
+③ 결재 [조직도]를 한 번 더 누른다
+④ 조직도에서 군수·부군수와 재난안전과를 펼쳐 본다
+⑤ [기본값]을 눌러 기본 결재선을 본다
+⑥ [취소]로 닫는다 — [상신]은 누르지 않는다</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>조직도는 한 번에 하나만 열리고 다시 누르면 닫힌다. 군수·부군수도 있다. QA박안전1 본인 옆에는 «기안자», 이미 고른 사람 옆에는 «검토 지정됨»·«결재 지정됨»이 붙고 고를 수 없다. 기본 결재선의 검토·결재 칸에 QA박안전1 본인이 없다(못 찾은 칸은 비어 있다). «작성중» 점검표가 없으면 «확인 불가»</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="81" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전1(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>인력·예산 &gt; 예산 총괄표</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>상신된 문서의 기안자는 바뀌지 않는다</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>① 내가 상신하지 않은 상신된(승인완료) 점검표를 연다
+② 결재 상태 창을 열고 «결재선:» 줄과 이력 표의 «결재 상신» 줄만 본다
+③ [닫기]</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>«결재선: 기안 ○○»의 ○○이 같은 창 이력 표의 «결재 상신» 처리자와 같고, 내 계정 이름(QA박안전1)으로 바뀌어 있지 않다. 상신된(승인완료) 점검표가 없으면 «확인 불가»</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G4:G7">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"성공"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+      <formula>"실패"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
+      <formula>"오류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
+      <formula>"보류"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
+      <formula>"확인 불가"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="6">
+      <formula>"문의"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H7">
+    <cfRule type="expression" priority="7" dxfId="7">
+      <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G4:G7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+      <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2388,7 +2322,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2408,7 +2342,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
+          <t>🗂 QA박안전1 창에서 합니다. 12번에서 만드는 것에는 내 이름을 붙이고 끝나면 지웁니다.</t>
         </is>
       </c>
     </row>
@@ -2459,13 +2393,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2480,30 +2414,30 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>필수 칸을 비우고 저장해 본다</t>
+          <t>등록 창 3곳(예: 수시 위험성평가 등록 · 협의체 운영 결과 등록 · 의견 등록)에서 필수 칸을 비우고 저장해 본다 → [취소]로 닫는다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>무엇을 채울지 알려 주고 이미 적은 값은 지워지지 않는다</t>
+          <t>무엇을 채울지 알려 주고 이미 적은 값은 지워지지 않는다. 빈 채로 저장되면 «실패»</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>등록 창</t>
+          <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -2513,7 +2447,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>값을 적고 [취소] → 다시 연다 / 적은 채로 다른 메뉴로 간다</t>
+          <t>① [＋ 수시평가 등록] → 사유를 골라 등록 창에서 내용을 적고 [취소] → 다시 연다
+② 값을 적은 채 다른 메뉴로 갔다가 돌아온다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2525,18 +2460,18 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>아무 화면</t>
+          <t>안전보건교육 &gt; 교육 현황·관리 &gt; 근로자 명단 관리</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -2546,25 +2481,28 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>무언가 등록 → 새로고침 → 뒤로 → 앞으로</t>
+          <t>① [＋ 직접 등록]에서 이름 «윤성현_새로고침», 부서는 내 부서(물순환사업소)로 넣고 [등록]
+② 새로고침(F5)
+③ 브라우저 [뒤로] → [앞으로]
+④ 끝나면 내 줄의 [삭제] → 확인</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>오류가 없고 저장한 값이 남아 있다</t>
+          <t>오류가 없고 «윤성현_새로고침» 줄이 계속 남아 있다. 삭제하면 그 줄만 사라진다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2579,12 +2517,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>파일 이름 누르기 · 양식 내려받기 · PDF 출력 등 3곳</t>
+          <t>파일 이름 누르기 · 양식 내려받기 · PDF 출력 등 3곳을 눌러 본다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>«…후 제공됩니다»처럼 알려 준다. 저장이 안 됐는데 «저장했습니다»가 뜨면 실패</t>
+          <t>파일이 실제로 열리거나, 안 되는 기능이면 «…후 제공됩니다»처럼 알려 준다. 아무 일도 없거나, 저장이 안 됐는데 «저장했습니다»가 뜨면 실패</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
@@ -2593,11 +2531,11 @@
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -2626,11 +2564,11 @@
     </row>
     <row r="9" ht="51" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2645,12 +2583,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>브라우저 창을 좁게(휴대폰 폭까지) 줄인다</t>
+          <t>① 브라우저 창을 좁게(휴대폰 폭까지) 줄인다
+② 왼쪽 위 메뉴 버튼(줄 세 개)을 누른다</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>글자·버튼이 겹치지 않고 화면 전체가 옆으로 밀리지 않는다. 좁아지면 햄버거 메뉴와 «다른 메뉴»가 나온다</t>
+          <t>글자·버튼이 겹치지 않고 화면 전체가 옆으로 밀리지 않는다. 메뉴 버튼을 누르면 왼쪽 메뉴 아래에 «다른 메뉴»가 있다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
@@ -2659,11 +2598,11 @@
     </row>
     <row r="10" ht="51" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전1(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2678,7 +2617,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>메뉴 11개를 돌며 버튼·안내 문구를 본다</t>
+          <t>맨 위 메뉴를 모두 돌며 버튼·안내 문구를 본다</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -2808,7 +2747,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
